--- a/franquicias/ejemplo.xlsx
+++ b/franquicias/ejemplo.xlsx
@@ -32,22 +32,22 @@
     <t>CANTIDAD</t>
   </si>
   <si>
-    <t>XZST09-004-0136</t>
-  </si>
-  <si>
-    <t>XLLV23-105-18</t>
-  </si>
-  <si>
-    <t>XV-ER-CGC  11</t>
-  </si>
-  <si>
-    <t>XM3WRL00R4318</t>
-  </si>
-  <si>
-    <t>XCBH03-632-</t>
-  </si>
-  <si>
-    <t>XLLV18-428-18</t>
+    <t>XV3WSI04Z010138</t>
+  </si>
+  <si>
+    <t>XV5WDC26C0101</t>
+  </si>
+  <si>
+    <t>XV5SST14Z070237</t>
+  </si>
+  <si>
+    <t>XV4WSI02Z110136</t>
+  </si>
+  <si>
+    <t>XT2WBE19P0925</t>
+  </si>
+  <si>
+    <t>XT1WUD04B0692</t>
   </si>
 </sst>
 </file>
